--- a/artfynd/A 57940-2024 artfynd.xlsx
+++ b/artfynd/A 57940-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333830</v>
+        <v>123333811</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519101</v>
+        <v>519141</v>
       </c>
       <c r="R2" t="n">
-        <v>7002823</v>
+        <v>7002917</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +785,7 @@
         <v>123333810</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333814</v>
+        <v>123333813</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519127</v>
+        <v>519118</v>
       </c>
       <c r="R4" t="n">
-        <v>7002873</v>
+        <v>7002904</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333829</v>
+        <v>123333815</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519136</v>
+        <v>519092</v>
       </c>
       <c r="R5" t="n">
-        <v>7002961</v>
+        <v>7002845</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333828</v>
+        <v>123333812</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519140</v>
+        <v>519124</v>
       </c>
       <c r="R6" t="n">
-        <v>7002970</v>
+        <v>7002914</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333815</v>
+        <v>123333828</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519092</v>
+        <v>519140</v>
       </c>
       <c r="R7" t="n">
-        <v>7002845</v>
+        <v>7002970</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333811</v>
+        <v>123333814</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519141</v>
+        <v>519127</v>
       </c>
       <c r="R8" t="n">
-        <v>7002917</v>
+        <v>7002873</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333813</v>
+        <v>123333830</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519118</v>
+        <v>519101</v>
       </c>
       <c r="R9" t="n">
-        <v>7002904</v>
+        <v>7002823</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333812</v>
+        <v>123333829</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519124</v>
+        <v>519136</v>
       </c>
       <c r="R10" t="n">
-        <v>7002914</v>
+        <v>7002961</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 57940-2024 artfynd.xlsx
+++ b/artfynd/A 57940-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333811</v>
+        <v>123333813</v>
       </c>
       <c r="B2" t="n">
         <v>57481</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519141</v>
+        <v>519118</v>
       </c>
       <c r="R2" t="n">
-        <v>7002917</v>
+        <v>7002904</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333810</v>
+        <v>123333815</v>
       </c>
       <c r="B3" t="n">
         <v>57481</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519137</v>
+        <v>519092</v>
       </c>
       <c r="R3" t="n">
-        <v>7002969</v>
+        <v>7002845</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333813</v>
+        <v>123333814</v>
       </c>
       <c r="B4" t="n">
         <v>57481</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519118</v>
+        <v>519127</v>
       </c>
       <c r="R4" t="n">
-        <v>7002904</v>
+        <v>7002873</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333815</v>
+        <v>123333830</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519092</v>
+        <v>519101</v>
       </c>
       <c r="R5" t="n">
-        <v>7002845</v>
+        <v>7002823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333812</v>
+        <v>123333829</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519124</v>
+        <v>519136</v>
       </c>
       <c r="R6" t="n">
-        <v>7002914</v>
+        <v>7002961</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333828</v>
+        <v>123333811</v>
       </c>
       <c r="B7" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519140</v>
+        <v>519141</v>
       </c>
       <c r="R7" t="n">
-        <v>7002970</v>
+        <v>7002917</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333814</v>
+        <v>123333812</v>
       </c>
       <c r="B8" t="n">
         <v>57481</v>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519127</v>
+        <v>519124</v>
       </c>
       <c r="R8" t="n">
-        <v>7002873</v>
+        <v>7002914</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333830</v>
+        <v>123333828</v>
       </c>
       <c r="B9" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519101</v>
+        <v>519140</v>
       </c>
       <c r="R9" t="n">
-        <v>7002823</v>
+        <v>7002970</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333829</v>
+        <v>123333810</v>
       </c>
       <c r="B10" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519136</v>
+        <v>519137</v>
       </c>
       <c r="R10" t="n">
-        <v>7002961</v>
+        <v>7002969</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 57940-2024 artfynd.xlsx
+++ b/artfynd/A 57940-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333813</v>
+        <v>123333828</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519118</v>
+        <v>519140</v>
       </c>
       <c r="R2" t="n">
-        <v>7002904</v>
+        <v>7002970</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333815</v>
+        <v>123333830</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519092</v>
+        <v>519101</v>
       </c>
       <c r="R3" t="n">
-        <v>7002845</v>
+        <v>7002823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -996,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333830</v>
+        <v>123333815</v>
       </c>
       <c r="B5" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519101</v>
+        <v>519092</v>
       </c>
       <c r="R5" t="n">
-        <v>7002823</v>
+        <v>7002845</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,7 +1096,7 @@
         <v>123333829</v>
       </c>
       <c r="B6" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1200,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333811</v>
+        <v>123333812</v>
       </c>
       <c r="B7" t="n">
         <v>57481</v>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519141</v>
+        <v>519124</v>
       </c>
       <c r="R7" t="n">
-        <v>7002917</v>
+        <v>7002914</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1275,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333812</v>
+        <v>123333813</v>
       </c>
       <c r="B8" t="n">
         <v>57481</v>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519124</v>
+        <v>519118</v>
       </c>
       <c r="R8" t="n">
-        <v>7002914</v>
+        <v>7002904</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333828</v>
+        <v>123333811</v>
       </c>
       <c r="B9" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519140</v>
+        <v>519141</v>
       </c>
       <c r="R9" t="n">
-        <v>7002970</v>
+        <v>7002917</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 57940-2024 artfynd.xlsx
+++ b/artfynd/A 57940-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333830</v>
+        <v>123333811</v>
       </c>
       <c r="B2" t="n">
-        <v>79856</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519101</v>
+        <v>519141</v>
       </c>
       <c r="R2" t="n">
-        <v>7002823</v>
+        <v>7002917</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333828</v>
+        <v>123333815</v>
       </c>
       <c r="B3" t="n">
-        <v>79856</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519140</v>
+        <v>519092</v>
       </c>
       <c r="R3" t="n">
-        <v>7002970</v>
+        <v>7002845</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333810</v>
+        <v>123333812</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519137</v>
+        <v>519124</v>
       </c>
       <c r="R4" t="n">
-        <v>7002969</v>
+        <v>7002914</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333812</v>
+        <v>123333813</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519124</v>
+        <v>519118</v>
       </c>
       <c r="R5" t="n">
-        <v>7002914</v>
+        <v>7002904</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333814</v>
+        <v>123333829</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>79862</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519127</v>
+        <v>519136</v>
       </c>
       <c r="R6" t="n">
-        <v>7002873</v>
+        <v>7002961</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333815</v>
+        <v>123333814</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519092</v>
+        <v>519127</v>
       </c>
       <c r="R7" t="n">
-        <v>7002845</v>
+        <v>7002873</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333813</v>
+        <v>123333810</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519118</v>
+        <v>519137</v>
       </c>
       <c r="R8" t="n">
-        <v>7002904</v>
+        <v>7002969</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333829</v>
+        <v>123333830</v>
       </c>
       <c r="B9" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519136</v>
+        <v>519101</v>
       </c>
       <c r="R9" t="n">
-        <v>7002961</v>
+        <v>7002823</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333811</v>
+        <v>123333828</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>79862</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519141</v>
+        <v>519140</v>
       </c>
       <c r="R10" t="n">
-        <v>7002917</v>
+        <v>7002970</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 57940-2024 artfynd.xlsx
+++ b/artfynd/A 57940-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333811</v>
+        <v>123333813</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519141</v>
+        <v>519118</v>
       </c>
       <c r="R2" t="n">
-        <v>7002917</v>
+        <v>7002904</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333815</v>
+        <v>123333812</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519092</v>
+        <v>519124</v>
       </c>
       <c r="R3" t="n">
-        <v>7002845</v>
+        <v>7002914</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333812</v>
+        <v>123333815</v>
       </c>
       <c r="B4" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519124</v>
+        <v>519092</v>
       </c>
       <c r="R4" t="n">
-        <v>7002914</v>
+        <v>7002845</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333813</v>
+        <v>123333811</v>
       </c>
       <c r="B5" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519118</v>
+        <v>519141</v>
       </c>
       <c r="R5" t="n">
-        <v>7002904</v>
+        <v>7002917</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>123333829</v>
       </c>
       <c r="B6" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333814</v>
+        <v>123333830</v>
       </c>
       <c r="B7" t="n">
-        <v>57487</v>
+        <v>79867</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519127</v>
+        <v>519101</v>
       </c>
       <c r="R7" t="n">
-        <v>7002873</v>
+        <v>7002823</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333810</v>
+        <v>123333814</v>
       </c>
       <c r="B8" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519137</v>
+        <v>519127</v>
       </c>
       <c r="R8" t="n">
-        <v>7002969</v>
+        <v>7002873</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333830</v>
+        <v>123333810</v>
       </c>
       <c r="B9" t="n">
-        <v>79862</v>
+        <v>57490</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519101</v>
+        <v>519137</v>
       </c>
       <c r="R9" t="n">
-        <v>7002823</v>
+        <v>7002969</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,7 +1524,7 @@
         <v>123333828</v>
       </c>
       <c r="B10" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 57940-2024 artfynd.xlsx
+++ b/artfynd/A 57940-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333813</v>
+        <v>123333829</v>
       </c>
       <c r="B2" t="n">
-        <v>57490</v>
+        <v>79869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519118</v>
+        <v>519136</v>
       </c>
       <c r="R2" t="n">
-        <v>7002904</v>
+        <v>7002961</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333812</v>
+        <v>123333813</v>
       </c>
       <c r="B3" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519124</v>
+        <v>519118</v>
       </c>
       <c r="R3" t="n">
-        <v>7002914</v>
+        <v>7002904</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333815</v>
+        <v>123333814</v>
       </c>
       <c r="B4" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519092</v>
+        <v>519127</v>
       </c>
       <c r="R4" t="n">
-        <v>7002845</v>
+        <v>7002873</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333811</v>
+        <v>123333830</v>
       </c>
       <c r="B5" t="n">
-        <v>57490</v>
+        <v>79869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519141</v>
+        <v>519101</v>
       </c>
       <c r="R5" t="n">
-        <v>7002917</v>
+        <v>7002823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333829</v>
+        <v>123333810</v>
       </c>
       <c r="B6" t="n">
-        <v>79867</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519136</v>
+        <v>519137</v>
       </c>
       <c r="R6" t="n">
-        <v>7002961</v>
+        <v>7002969</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333830</v>
+        <v>123333811</v>
       </c>
       <c r="B7" t="n">
-        <v>79867</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519101</v>
+        <v>519141</v>
       </c>
       <c r="R7" t="n">
-        <v>7002823</v>
+        <v>7002917</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333814</v>
+        <v>123333815</v>
       </c>
       <c r="B8" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519127</v>
+        <v>519092</v>
       </c>
       <c r="R8" t="n">
-        <v>7002873</v>
+        <v>7002845</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333810</v>
+        <v>123333812</v>
       </c>
       <c r="B9" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519137</v>
+        <v>519124</v>
       </c>
       <c r="R9" t="n">
-        <v>7002969</v>
+        <v>7002914</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,7 +1524,7 @@
         <v>123333828</v>
       </c>
       <c r="B10" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 57940-2024 artfynd.xlsx
+++ b/artfynd/A 57940-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333829</v>
+        <v>123333812</v>
       </c>
       <c r="B2" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519136</v>
+        <v>519124</v>
       </c>
       <c r="R2" t="n">
-        <v>7002961</v>
+        <v>7002914</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333814</v>
+        <v>123333830</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519127</v>
+        <v>519101</v>
       </c>
       <c r="R4" t="n">
-        <v>7002873</v>
+        <v>7002823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333830</v>
+        <v>123333828</v>
       </c>
       <c r="B5" t="n">
         <v>79869</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519101</v>
+        <v>519140</v>
       </c>
       <c r="R5" t="n">
-        <v>7002823</v>
+        <v>7002970</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333810</v>
+        <v>123333815</v>
       </c>
       <c r="B6" t="n">
         <v>57491</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519137</v>
+        <v>519092</v>
       </c>
       <c r="R6" t="n">
-        <v>7002969</v>
+        <v>7002845</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333811</v>
+        <v>123333810</v>
       </c>
       <c r="B7" t="n">
         <v>57491</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519141</v>
+        <v>519137</v>
       </c>
       <c r="R7" t="n">
-        <v>7002917</v>
+        <v>7002969</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333815</v>
+        <v>123333811</v>
       </c>
       <c r="B8" t="n">
         <v>57491</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519092</v>
+        <v>519141</v>
       </c>
       <c r="R8" t="n">
-        <v>7002845</v>
+        <v>7002917</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333812</v>
+        <v>123333814</v>
       </c>
       <c r="B9" t="n">
         <v>57491</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519124</v>
+        <v>519127</v>
       </c>
       <c r="R9" t="n">
-        <v>7002914</v>
+        <v>7002873</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333828</v>
+        <v>123333829</v>
       </c>
       <c r="B10" t="n">
         <v>79869</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519140</v>
+        <v>519136</v>
       </c>
       <c r="R10" t="n">
-        <v>7002970</v>
+        <v>7002961</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 57940-2024 artfynd.xlsx
+++ b/artfynd/A 57940-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333812</v>
+        <v>123333814</v>
       </c>
       <c r="B2" t="n">
         <v>57491</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519124</v>
+        <v>519127</v>
       </c>
       <c r="R2" t="n">
-        <v>7002914</v>
+        <v>7002873</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333813</v>
+        <v>123333828</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519118</v>
+        <v>519140</v>
       </c>
       <c r="R3" t="n">
-        <v>7002904</v>
+        <v>7002970</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333830</v>
+        <v>123333811</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519101</v>
+        <v>519141</v>
       </c>
       <c r="R4" t="n">
-        <v>7002823</v>
+        <v>7002917</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333828</v>
+        <v>123333829</v>
       </c>
       <c r="B5" t="n">
         <v>79869</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519140</v>
+        <v>519136</v>
       </c>
       <c r="R5" t="n">
-        <v>7002970</v>
+        <v>7002961</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333815</v>
+        <v>123333830</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519092</v>
+        <v>519101</v>
       </c>
       <c r="R6" t="n">
-        <v>7002845</v>
+        <v>7002823</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333811</v>
+        <v>123333815</v>
       </c>
       <c r="B8" t="n">
         <v>57491</v>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519141</v>
+        <v>519092</v>
       </c>
       <c r="R8" t="n">
-        <v>7002917</v>
+        <v>7002845</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333814</v>
+        <v>123333813</v>
       </c>
       <c r="B9" t="n">
         <v>57491</v>
@@ -1454,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519127</v>
+        <v>519118</v>
       </c>
       <c r="R9" t="n">
-        <v>7002873</v>
+        <v>7002904</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1489,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333829</v>
+        <v>123333812</v>
       </c>
       <c r="B10" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519136</v>
+        <v>519124</v>
       </c>
       <c r="R10" t="n">
-        <v>7002961</v>
+        <v>7002914</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 57940-2024 artfynd.xlsx
+++ b/artfynd/A 57940-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333814</v>
+        <v>123333811</v>
       </c>
       <c r="B2" t="n">
         <v>57491</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519127</v>
+        <v>519141</v>
       </c>
       <c r="R2" t="n">
-        <v>7002873</v>
+        <v>7002917</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333828</v>
+        <v>123333815</v>
       </c>
       <c r="B3" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519140</v>
+        <v>519092</v>
       </c>
       <c r="R3" t="n">
-        <v>7002970</v>
+        <v>7002845</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333811</v>
+        <v>123333829</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519141</v>
+        <v>519136</v>
       </c>
       <c r="R4" t="n">
-        <v>7002917</v>
+        <v>7002961</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333829</v>
+        <v>123333830</v>
       </c>
       <c r="B5" t="n">
         <v>79869</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519136</v>
+        <v>519101</v>
       </c>
       <c r="R5" t="n">
-        <v>7002961</v>
+        <v>7002823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333830</v>
+        <v>123333812</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519101</v>
+        <v>519124</v>
       </c>
       <c r="R6" t="n">
-        <v>7002823</v>
+        <v>7002914</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333810</v>
+        <v>123333814</v>
       </c>
       <c r="B7" t="n">
         <v>57491</v>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519137</v>
+        <v>519127</v>
       </c>
       <c r="R7" t="n">
-        <v>7002969</v>
+        <v>7002873</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333815</v>
+        <v>123333828</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519092</v>
+        <v>519140</v>
       </c>
       <c r="R8" t="n">
-        <v>7002845</v>
+        <v>7002970</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333812</v>
+        <v>123333810</v>
       </c>
       <c r="B10" t="n">
         <v>57491</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519124</v>
+        <v>519137</v>
       </c>
       <c r="R10" t="n">
-        <v>7002914</v>
+        <v>7002969</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 57940-2024 artfynd.xlsx
+++ b/artfynd/A 57940-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333811</v>
+        <v>123333810</v>
       </c>
       <c r="B2" t="n">
         <v>57491</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519141</v>
+        <v>519137</v>
       </c>
       <c r="R2" t="n">
-        <v>7002917</v>
+        <v>7002969</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333815</v>
+        <v>123333830</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519092</v>
+        <v>519101</v>
       </c>
       <c r="R3" t="n">
-        <v>7002845</v>
+        <v>7002823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333829</v>
+        <v>123333828</v>
       </c>
       <c r="B4" t="n">
         <v>79869</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519136</v>
+        <v>519140</v>
       </c>
       <c r="R4" t="n">
-        <v>7002961</v>
+        <v>7002970</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333830</v>
+        <v>123333812</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519101</v>
+        <v>519124</v>
       </c>
       <c r="R5" t="n">
-        <v>7002823</v>
+        <v>7002914</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333812</v>
+        <v>123333814</v>
       </c>
       <c r="B6" t="n">
         <v>57491</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519124</v>
+        <v>519127</v>
       </c>
       <c r="R6" t="n">
-        <v>7002914</v>
+        <v>7002873</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333814</v>
+        <v>123333815</v>
       </c>
       <c r="B7" t="n">
         <v>57491</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519127</v>
+        <v>519092</v>
       </c>
       <c r="R7" t="n">
-        <v>7002873</v>
+        <v>7002845</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333828</v>
+        <v>123333811</v>
       </c>
       <c r="B8" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519140</v>
+        <v>519141</v>
       </c>
       <c r="R8" t="n">
-        <v>7002970</v>
+        <v>7002917</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333813</v>
+        <v>123333829</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519118</v>
+        <v>519136</v>
       </c>
       <c r="R9" t="n">
-        <v>7002904</v>
+        <v>7002961</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333810</v>
+        <v>123333813</v>
       </c>
       <c r="B10" t="n">
         <v>57491</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519137</v>
+        <v>519118</v>
       </c>
       <c r="R10" t="n">
-        <v>7002969</v>
+        <v>7002904</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 57940-2024 artfynd.xlsx
+++ b/artfynd/A 57940-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333810</v>
+        <v>123333811</v>
       </c>
       <c r="B2" t="n">
         <v>57491</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519137</v>
+        <v>519141</v>
       </c>
       <c r="R2" t="n">
-        <v>7002969</v>
+        <v>7002917</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333828</v>
+        <v>123333813</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519140</v>
+        <v>519118</v>
       </c>
       <c r="R4" t="n">
-        <v>7002970</v>
+        <v>7002904</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333812</v>
+        <v>123333810</v>
       </c>
       <c r="B5" t="n">
         <v>57491</v>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519124</v>
+        <v>519137</v>
       </c>
       <c r="R5" t="n">
-        <v>7002914</v>
+        <v>7002969</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333814</v>
+        <v>123333812</v>
       </c>
       <c r="B6" t="n">
         <v>57491</v>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519127</v>
+        <v>519124</v>
       </c>
       <c r="R6" t="n">
-        <v>7002873</v>
+        <v>7002914</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333815</v>
+        <v>123333828</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519092</v>
+        <v>519140</v>
       </c>
       <c r="R7" t="n">
-        <v>7002845</v>
+        <v>7002970</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333811</v>
+        <v>123333829</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519141</v>
+        <v>519136</v>
       </c>
       <c r="R8" t="n">
-        <v>7002917</v>
+        <v>7002961</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333829</v>
+        <v>123333814</v>
       </c>
       <c r="B9" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519136</v>
+        <v>519127</v>
       </c>
       <c r="R9" t="n">
-        <v>7002961</v>
+        <v>7002873</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333813</v>
+        <v>123333815</v>
       </c>
       <c r="B10" t="n">
         <v>57491</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519118</v>
+        <v>519092</v>
       </c>
       <c r="R10" t="n">
-        <v>7002904</v>
+        <v>7002845</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 57940-2024 artfynd.xlsx
+++ b/artfynd/A 57940-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333811</v>
+        <v>123333828</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519141</v>
+        <v>519140</v>
       </c>
       <c r="R2" t="n">
-        <v>7002917</v>
+        <v>7002970</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333830</v>
+        <v>123333829</v>
       </c>
       <c r="B3" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519101</v>
+        <v>519136</v>
       </c>
       <c r="R3" t="n">
-        <v>7002823</v>
+        <v>7002961</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333813</v>
+        <v>123333830</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519118</v>
+        <v>519101</v>
       </c>
       <c r="R4" t="n">
-        <v>7002904</v>
+        <v>7002823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,12 +969,7 @@
         <v>123333810</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,15 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333812</v>
+        <v>123333811</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519124</v>
+        <v>519141</v>
       </c>
       <c r="R6" t="n">
-        <v>7002914</v>
+        <v>7002917</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1143,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,15 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333828</v>
+        <v>123333812</v>
       </c>
       <c r="B7" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519140</v>
+        <v>519124</v>
       </c>
       <c r="R7" t="n">
-        <v>7002970</v>
+        <v>7002914</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,15 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333829</v>
+        <v>123333813</v>
       </c>
       <c r="B8" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519136</v>
+        <v>519118</v>
       </c>
       <c r="R8" t="n">
-        <v>7002961</v>
+        <v>7002904</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,6 +1343,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,12 +1377,7 @@
         <v>123333814</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,12 +1479,7 @@
         <v>123333815</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 57940-2024 artfynd.xlsx
+++ b/artfynd/A 57940-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333828</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333829</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333830</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333810</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333811</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,6 +1299,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333812</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333813</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333814</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,8 +1620,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333815</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>